--- a/Perfil_Mentoria.xlsx
+++ b/Perfil_Mentoria.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://muvamozorg.sharepoint.com/sites/mis.drive/Documentos Partilhados/PROJECTOS/Sistema de Monitoria/NEXUS/2026/Dash_Nexus/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="34" documentId="11_E693E059F159B3A8EDF5CA209B888B5094EB2656" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{58C12EC3-CC31-4B60-B93C-280DC52D9DAF}"/>
+  <xr:revisionPtr revIDLastSave="36" documentId="11_E693E059F159B3A8EDF5CA209B888B5094EB2656" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2862E968-7A94-4458-BA41-D0F4CDEBF480}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -7822,21 +7822,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:BU377"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="43.77734375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="43.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.28515625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="17" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="29.6640625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="16.21875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.44140625" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="33.44140625" bestFit="1" customWidth="1"/>
-    <col min="62" max="62" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="29.7109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="33.42578125" bestFit="1" customWidth="1"/>
+    <col min="62" max="62" width="13.28515625" bestFit="1" customWidth="1"/>
     <col min="70" max="70" width="24" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:73" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:73" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -8057,7 +8058,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="2" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>72</v>
       </c>
@@ -8188,7 +8189,7 @@
         <v>1219</v>
       </c>
     </row>
-    <row r="3" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>72</v>
       </c>
@@ -8358,7 +8359,7 @@
         <v>1177</v>
       </c>
     </row>
-    <row r="4" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>72</v>
       </c>
@@ -8486,7 +8487,7 @@
         <v>979</v>
       </c>
     </row>
-    <row r="5" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>72</v>
       </c>
@@ -8623,7 +8624,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="6" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>72</v>
       </c>
@@ -8769,7 +8770,7 @@
         <v>1064</v>
       </c>
     </row>
-    <row r="7" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>72</v>
       </c>
@@ -8897,7 +8898,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="8" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>72</v>
       </c>
@@ -9031,7 +9032,7 @@
         <v>629</v>
       </c>
     </row>
-    <row r="9" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>72</v>
       </c>
@@ -9174,7 +9175,7 @@
         <v>801</v>
       </c>
     </row>
-    <row r="10" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>72</v>
       </c>
@@ -9293,7 +9294,7 @@
         <v>703</v>
       </c>
     </row>
-    <row r="11" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>72</v>
       </c>
@@ -9418,7 +9419,7 @@
         <v>933</v>
       </c>
     </row>
-    <row r="12" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>72</v>
       </c>
@@ -9543,7 +9544,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="13" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>72</v>
       </c>
@@ -9689,7 +9690,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="14" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>72</v>
       </c>
@@ -9841,7 +9842,7 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="15" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>72</v>
       </c>
@@ -9990,7 +9991,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="16" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>72</v>
       </c>
@@ -10133,7 +10134,7 @@
         <v>1283</v>
       </c>
     </row>
-    <row r="17" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>72</v>
       </c>
@@ -10264,7 +10265,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="18" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>72</v>
       </c>
@@ -10386,7 +10387,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="19" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>72</v>
       </c>
@@ -10514,7 +10515,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="20" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>72</v>
       </c>
@@ -10636,7 +10637,7 @@
         <v>1277</v>
       </c>
     </row>
-    <row r="21" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>72</v>
       </c>
@@ -10806,7 +10807,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="22" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>72</v>
       </c>
@@ -10970,7 +10971,7 @@
         <v>904</v>
       </c>
     </row>
-    <row r="23" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>72</v>
       </c>
@@ -11110,7 +11111,7 @@
         <v>673</v>
       </c>
     </row>
-    <row r="24" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>72</v>
       </c>
@@ -11256,7 +11257,7 @@
         <v>750</v>
       </c>
     </row>
-    <row r="25" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>72</v>
       </c>
@@ -11396,7 +11397,7 @@
         <v>942</v>
       </c>
     </row>
-    <row r="26" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>72</v>
       </c>
@@ -11545,7 +11546,7 @@
         <v>1146</v>
       </c>
     </row>
-    <row r="27" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>72</v>
       </c>
@@ -11700,7 +11701,7 @@
         <v>686</v>
       </c>
     </row>
-    <row r="28" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>72</v>
       </c>
@@ -11810,7 +11811,7 @@
         <v>691</v>
       </c>
     </row>
-    <row r="29" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>72</v>
       </c>
@@ -11935,7 +11936,7 @@
         <v>823</v>
       </c>
     </row>
-    <row r="30" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>72</v>
       </c>
@@ -12054,7 +12055,7 @@
         <v>697</v>
       </c>
     </row>
-    <row r="31" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>72</v>
       </c>
@@ -12200,7 +12201,7 @@
         <v>850</v>
       </c>
     </row>
-    <row r="32" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>72</v>
       </c>
@@ -12328,7 +12329,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="33" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>72</v>
       </c>
@@ -12480,7 +12481,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="34" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>72</v>
       </c>
@@ -12617,7 +12618,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="35" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>72</v>
       </c>
@@ -12778,7 +12779,7 @@
         <v>710</v>
       </c>
     </row>
-    <row r="36" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>72</v>
       </c>
@@ -12909,7 +12910,7 @@
         <v>862</v>
       </c>
     </row>
-    <row r="37" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>72</v>
       </c>
@@ -13067,7 +13068,7 @@
         <v>725</v>
       </c>
     </row>
-    <row r="38" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>72</v>
       </c>
@@ -13225,7 +13226,7 @@
         <v>743</v>
       </c>
     </row>
-    <row r="39" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>72</v>
       </c>
@@ -13401,7 +13402,7 @@
         <v>869</v>
       </c>
     </row>
-    <row r="40" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>72</v>
       </c>
@@ -13556,7 +13557,7 @@
         <v>834</v>
       </c>
     </row>
-    <row r="41" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>72</v>
       </c>
@@ -13714,7 +13715,7 @@
         <v>876</v>
       </c>
     </row>
-    <row r="42" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>72</v>
       </c>
@@ -13884,7 +13885,7 @@
         <v>829</v>
       </c>
     </row>
-    <row r="43" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>72</v>
       </c>
@@ -14036,7 +14037,7 @@
         <v>928</v>
       </c>
     </row>
-    <row r="44" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>72</v>
       </c>
@@ -14170,7 +14171,7 @@
         <v>640</v>
       </c>
     </row>
-    <row r="45" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>72</v>
       </c>
@@ -14328,7 +14329,7 @@
         <v>844</v>
       </c>
     </row>
-    <row r="46" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>72</v>
       </c>
@@ -14489,7 +14490,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="47" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>72</v>
       </c>
@@ -14623,7 +14624,7 @@
         <v>519</v>
       </c>
     </row>
-    <row r="48" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>72</v>
       </c>
@@ -14760,7 +14761,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="49" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>72</v>
       </c>
@@ -14921,7 +14922,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="50" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>72</v>
       </c>
@@ -15085,7 +15086,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="51" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>72</v>
       </c>
@@ -15234,7 +15235,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="52" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>72</v>
       </c>
@@ -15407,7 +15408,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="53" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>72</v>
       </c>
@@ -15562,7 +15563,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="54" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>72</v>
       </c>
@@ -15720,7 +15721,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="55" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>72</v>
       </c>
@@ -15875,7 +15876,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="56" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>72</v>
       </c>
@@ -16042,7 +16043,7 @@
         <v>1298</v>
       </c>
     </row>
-    <row r="57" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>72</v>
       </c>
@@ -16215,7 +16216,7 @@
         <v>1242</v>
       </c>
     </row>
-    <row r="58" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>72</v>
       </c>
@@ -16352,7 +16353,7 @@
         <v>1087</v>
       </c>
     </row>
-    <row r="59" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>72</v>
       </c>
@@ -16513,7 +16514,7 @@
         <v>1111</v>
       </c>
     </row>
-    <row r="60" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>72</v>
       </c>
@@ -16662,7 +16663,7 @@
         <v>1026</v>
       </c>
     </row>
-    <row r="61" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>72</v>
       </c>
@@ -16811,7 +16812,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="62" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>72</v>
       </c>
@@ -16981,7 +16982,7 @@
         <v>1254</v>
       </c>
     </row>
-    <row r="63" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>72</v>
       </c>
@@ -17118,7 +17119,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="64" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>72</v>
       </c>
@@ -17297,7 +17298,7 @@
         <v>1127</v>
       </c>
     </row>
-    <row r="65" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>72</v>
       </c>
@@ -17440,7 +17441,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="66" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>72</v>
       </c>
@@ -17619,7 +17620,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="67" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>72</v>
       </c>
@@ -17744,7 +17745,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="68" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>72</v>
       </c>
@@ -17887,7 +17888,7 @@
         <v>1203</v>
       </c>
     </row>
-    <row r="69" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>72</v>
       </c>
@@ -18042,7 +18043,7 @@
         <v>1141</v>
       </c>
     </row>
-    <row r="70" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>72</v>
       </c>
@@ -18191,7 +18192,7 @@
         <v>1053</v>
       </c>
     </row>
-    <row r="71" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>72</v>
       </c>
@@ -18346,7 +18347,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="72" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>72</v>
       </c>
@@ -18477,7 +18478,7 @@
         <v>1116</v>
       </c>
     </row>
-    <row r="73" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>72</v>
       </c>
@@ -18632,7 +18633,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="74" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>72</v>
       </c>
@@ -18790,7 +18791,7 @@
         <v>1034</v>
       </c>
     </row>
-    <row r="75" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>72</v>
       </c>
@@ -18897,7 +18898,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="76" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>72</v>
       </c>
@@ -19070,7 +19071,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="77" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>72</v>
       </c>
@@ -19252,7 +19253,7 @@
         <v>1005</v>
       </c>
     </row>
-    <row r="78" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>72</v>
       </c>
@@ -19404,7 +19405,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="79" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>72</v>
       </c>
@@ -19589,7 +19590,7 @@
         <v>992</v>
       </c>
     </row>
-    <row r="80" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>72</v>
       </c>
@@ -19753,7 +19754,7 @@
         <v>1021</v>
       </c>
     </row>
-    <row r="81" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>72</v>
       </c>
@@ -19896,7 +19897,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="82" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>72</v>
       </c>
@@ -20060,7 +20061,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="83" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>72</v>
       </c>
@@ -20215,7 +20216,7 @@
         <v>1197</v>
       </c>
     </row>
-    <row r="84" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>72</v>
       </c>
@@ -20370,7 +20371,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="85" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>72</v>
       </c>
@@ -20519,7 +20520,7 @@
         <v>966</v>
       </c>
     </row>
-    <row r="86" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>72</v>
       </c>
@@ -20674,7 +20675,7 @@
         <v>973</v>
       </c>
     </row>
-    <row r="87" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>72</v>
       </c>
@@ -20811,7 +20812,7 @@
         <v>1181</v>
       </c>
     </row>
-    <row r="88" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>72</v>
       </c>
@@ -20954,7 +20955,7 @@
         <v>952</v>
       </c>
     </row>
-    <row r="89" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>72</v>
       </c>
@@ -21100,7 +21101,7 @@
         <v>960</v>
       </c>
     </row>
-    <row r="90" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>72</v>
       </c>
@@ -21258,7 +21259,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="91" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>72</v>
       </c>
@@ -21428,7 +21429,7 @@
         <v>573</v>
       </c>
     </row>
-    <row r="92" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>72</v>
       </c>
@@ -21598,7 +21599,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="93" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>72</v>
       </c>
@@ -21759,7 +21760,7 @@
         <v>592</v>
       </c>
     </row>
-    <row r="94" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>72</v>
       </c>
@@ -21923,7 +21924,7 @@
         <v>896</v>
       </c>
     </row>
-    <row r="95" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>72</v>
       </c>
@@ -22081,7 +22082,7 @@
         <v>785</v>
       </c>
     </row>
-    <row r="96" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>72</v>
       </c>
@@ -22251,7 +22252,7 @@
         <v>1192</v>
       </c>
     </row>
-    <row r="97" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>72</v>
       </c>
@@ -22418,7 +22419,7 @@
         <v>1014</v>
       </c>
     </row>
-    <row r="98" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>72</v>
       </c>
@@ -22582,7 +22583,7 @@
         <v>985</v>
       </c>
     </row>
-    <row r="99" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>72</v>
       </c>
@@ -22746,7 +22747,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="100" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>72</v>
       </c>
@@ -22886,7 +22887,7 @@
         <v>611</v>
       </c>
     </row>
-    <row r="101" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>72</v>
       </c>
@@ -23047,7 +23048,7 @@
         <v>1048</v>
       </c>
     </row>
-    <row r="102" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>72</v>
       </c>
@@ -23190,7 +23191,7 @@
         <v>1059</v>
       </c>
     </row>
-    <row r="103" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>72</v>
       </c>
@@ -23372,7 +23373,7 @@
         <v>759</v>
       </c>
     </row>
-    <row r="104" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>72</v>
       </c>
@@ -23542,7 +23543,7 @@
         <v>1290</v>
       </c>
     </row>
-    <row r="105" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>72</v>
       </c>
@@ -23694,7 +23695,7 @@
         <v>856</v>
       </c>
     </row>
-    <row r="106" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>72</v>
       </c>
@@ -23843,7 +23844,7 @@
         <v>716</v>
       </c>
     </row>
-    <row r="107" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>72</v>
       </c>
@@ -23998,7 +23999,7 @@
         <v>669</v>
       </c>
     </row>
-    <row r="108" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>72</v>
       </c>
@@ -24180,7 +24181,7 @@
         <v>1104</v>
       </c>
     </row>
-    <row r="109" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>72</v>
       </c>
@@ -24347,7 +24348,7 @@
         <v>883</v>
       </c>
     </row>
-    <row r="110" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>72</v>
       </c>
@@ -24505,7 +24506,7 @@
         <v>1270</v>
       </c>
     </row>
-    <row r="111" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>72</v>
       </c>
@@ -24684,7 +24685,7 @@
         <v>1228</v>
       </c>
     </row>
-    <row r="112" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>72</v>
       </c>
@@ -24860,7 +24861,7 @@
         <v>1079</v>
       </c>
     </row>
-    <row r="113" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>72</v>
       </c>
@@ -25033,7 +25034,7 @@
         <v>766</v>
       </c>
     </row>
-    <row r="114" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>72</v>
       </c>
@@ -25191,7 +25192,7 @@
         <v>778</v>
       </c>
     </row>
-    <row r="115" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>72</v>
       </c>
@@ -25376,7 +25377,7 @@
         <v>1213</v>
       </c>
     </row>
-    <row r="116" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>72</v>
       </c>
@@ -25552,7 +25553,7 @@
         <v>817</v>
       </c>
     </row>
-    <row r="117" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>72</v>
       </c>
@@ -25704,7 +25705,7 @@
         <v>1091</v>
       </c>
     </row>
-    <row r="118" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>72</v>
       </c>
@@ -25871,7 +25872,7 @@
         <v>1042</v>
       </c>
     </row>
-    <row r="119" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>72</v>
       </c>
@@ -26023,7 +26024,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="120" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>72</v>
       </c>
@@ -26172,7 +26173,7 @@
         <v>1185</v>
       </c>
     </row>
-    <row r="121" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>72</v>
       </c>
@@ -26345,7 +26346,7 @@
         <v>1235</v>
       </c>
     </row>
-    <row r="122" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>72</v>
       </c>
@@ -26494,7 +26495,7 @@
         <v>1262</v>
       </c>
     </row>
-    <row r="123" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>72</v>
       </c>
@@ -26652,7 +26653,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="124" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>72</v>
       </c>
@@ -26789,7 +26790,7 @@
         <v>1134</v>
       </c>
     </row>
-    <row r="125" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>72</v>
       </c>
@@ -26929,7 +26930,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="126" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>72</v>
       </c>
@@ -27039,7 +27040,7 @@
         <v>995</v>
       </c>
     </row>
-    <row r="127" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>72</v>
       </c>
@@ -27167,7 +27168,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="128" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>72</v>
       </c>
@@ -27328,7 +27329,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="129" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>72</v>
       </c>
@@ -27498,7 +27499,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="130" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>72</v>
       </c>
@@ -27623,7 +27624,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="131" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>72</v>
       </c>
@@ -27751,7 +27752,7 @@
         <v>921</v>
       </c>
     </row>
-    <row r="132" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>72</v>
       </c>
@@ -27891,7 +27892,7 @@
         <v>916</v>
       </c>
     </row>
-    <row r="133" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>72</v>
       </c>
@@ -28007,7 +28008,7 @@
         <v>649</v>
       </c>
     </row>
-    <row r="134" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>72</v>
       </c>
@@ -28150,7 +28151,7 @@
         <v>806</v>
       </c>
     </row>
-    <row r="135" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>72</v>
       </c>
@@ -28290,7 +28291,7 @@
         <v>616</v>
       </c>
     </row>
-    <row r="136" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>72</v>
       </c>
@@ -28421,7 +28422,7 @@
         <v>679</v>
       </c>
     </row>
-    <row r="137" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>72</v>
       </c>
@@ -28549,7 +28550,7 @@
         <v>1097</v>
       </c>
     </row>
-    <row r="138" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>72</v>
       </c>
@@ -28680,7 +28681,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="139" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>72</v>
       </c>
@@ -28814,7 +28815,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="140" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>72</v>
       </c>
@@ -28945,7 +28946,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="141" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>72</v>
       </c>
@@ -29067,7 +29068,7 @@
         <v>794</v>
       </c>
     </row>
-    <row r="142" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>72</v>
       </c>
@@ -29195,7 +29196,7 @@
         <v>938</v>
       </c>
     </row>
-    <row r="143" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>72</v>
       </c>
@@ -29320,7 +29321,7 @@
         <v>598</v>
       </c>
     </row>
-    <row r="144" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>72</v>
       </c>
@@ -29448,7 +29449,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="145" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>72</v>
       </c>
@@ -29579,7 +29580,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="146" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>72</v>
       </c>
@@ -29722,7 +29723,7 @@
         <v>1073</v>
       </c>
     </row>
-    <row r="147" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>72</v>
       </c>
@@ -29838,7 +29839,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="148" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>72</v>
       </c>
@@ -29975,7 +29976,7 @@
         <v>1158</v>
       </c>
     </row>
-    <row r="149" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>72</v>
       </c>
@@ -30085,7 +30086,7 @@
         <v>735</v>
       </c>
     </row>
-    <row r="150" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>72</v>
       </c>
@@ -30240,7 +30241,7 @@
         <v>1248</v>
       </c>
     </row>
-    <row r="151" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>72</v>
       </c>
@@ -30356,7 +30357,7 @@
         <v>810</v>
       </c>
     </row>
-    <row r="152" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>72</v>
       </c>
@@ -30508,7 +30509,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="153" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>72</v>
       </c>
@@ -30624,7 +30625,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="154" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>72</v>
       </c>
@@ -30752,7 +30753,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="155" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>72</v>
       </c>
@@ -30874,7 +30875,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="156" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>72</v>
       </c>
@@ -31020,7 +31021,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="157" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>72</v>
       </c>
@@ -31148,7 +31149,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="158" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>72</v>
       </c>
@@ -31288,7 +31289,7 @@
         <v>788</v>
       </c>
     </row>
-    <row r="159" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>72</v>
       </c>
@@ -31416,7 +31417,7 @@
         <v>730</v>
       </c>
     </row>
-    <row r="160" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>72</v>
       </c>
@@ -31568,7 +31569,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="161" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>72</v>
       </c>
@@ -31681,7 +31682,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="162" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>72</v>
       </c>
@@ -31815,7 +31816,7 @@
         <v>662</v>
       </c>
     </row>
-    <row r="163" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>72</v>
       </c>
@@ -31943,7 +31944,7 @@
         <v>621</v>
       </c>
     </row>
-    <row r="164" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>72</v>
       </c>
@@ -32095,7 +32096,7 @@
         <v>773</v>
       </c>
     </row>
-    <row r="165" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>72</v>
       </c>
@@ -32223,7 +32224,7 @@
         <v>585</v>
       </c>
     </row>
-    <row r="166" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>72</v>
       </c>
@@ -32345,7 +32346,7 @@
         <v>1120</v>
       </c>
     </row>
-    <row r="167" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>72</v>
       </c>
@@ -32464,7 +32465,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="168" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
         <v>72</v>
       </c>
@@ -32595,7 +32596,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="169" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
         <v>72</v>
       </c>
@@ -32729,7 +32730,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="170" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
         <v>72</v>
       </c>
@@ -32851,7 +32852,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="171" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
         <v>72</v>
       </c>
@@ -32982,7 +32983,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="172" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
         <v>72</v>
       </c>
@@ -33107,7 +33108,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="173" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
         <v>72</v>
       </c>
@@ -33250,7 +33251,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="174" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
         <v>72</v>
       </c>
@@ -33402,7 +33403,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="175" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
         <v>72</v>
       </c>
@@ -33533,7 +33534,7 @@
         <v>635</v>
       </c>
     </row>
-    <row r="176" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
         <v>72</v>
       </c>
@@ -33679,7 +33680,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="177" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
         <v>72</v>
       </c>
@@ -33810,7 +33811,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="178" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
         <v>72</v>
       </c>
@@ -33956,7 +33957,7 @@
         <v>910</v>
       </c>
     </row>
-    <row r="179" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
         <v>1299</v>
       </c>
@@ -34111,7 +34112,7 @@
         <v>1542</v>
       </c>
     </row>
-    <row r="180" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
         <v>1299</v>
       </c>
@@ -34224,7 +34225,7 @@
         <v>1739</v>
       </c>
     </row>
-    <row r="181" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
         <v>1299</v>
       </c>
@@ -34355,7 +34356,7 @@
         <v>1706</v>
       </c>
     </row>
-    <row r="182" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
         <v>1299</v>
       </c>
@@ -34492,7 +34493,7 @@
         <v>2222</v>
       </c>
     </row>
-    <row r="183" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
         <v>1299</v>
       </c>
@@ -34623,7 +34624,7 @@
         <v>1308</v>
       </c>
     </row>
-    <row r="184" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
         <v>1299</v>
       </c>
@@ -34754,7 +34755,7 @@
         <v>1809</v>
       </c>
     </row>
-    <row r="185" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
         <v>1299</v>
       </c>
@@ -34909,7 +34910,7 @@
         <v>1478</v>
       </c>
     </row>
-    <row r="186" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
         <v>1299</v>
       </c>
@@ -35046,7 +35047,7 @@
         <v>1551</v>
       </c>
     </row>
-    <row r="187" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
         <v>1299</v>
       </c>
@@ -35177,7 +35178,7 @@
         <v>1736</v>
       </c>
     </row>
-    <row r="188" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
         <v>1299</v>
       </c>
@@ -35302,7 +35303,7 @@
         <v>1317</v>
       </c>
     </row>
-    <row r="189" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
         <v>1299</v>
       </c>
@@ -35442,7 +35443,7 @@
         <v>2247</v>
       </c>
     </row>
-    <row r="190" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
         <v>1299</v>
       </c>
@@ -35561,7 +35562,7 @@
         <v>2036</v>
       </c>
     </row>
-    <row r="191" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
         <v>1299</v>
       </c>
@@ -35686,7 +35687,7 @@
         <v>1629</v>
       </c>
     </row>
-    <row r="192" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
         <v>1299</v>
       </c>
@@ -35823,7 +35824,7 @@
         <v>2240</v>
       </c>
     </row>
-    <row r="193" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
         <v>1299</v>
       </c>
@@ -35954,7 +35955,7 @@
         <v>2100</v>
       </c>
     </row>
-    <row r="194" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
         <v>1299</v>
       </c>
@@ -36085,7 +36086,7 @@
         <v>1754</v>
       </c>
     </row>
-    <row r="195" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
         <v>1299</v>
       </c>
@@ -36243,7 +36244,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="196" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
         <v>1299</v>
       </c>
@@ -36374,7 +36375,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="197" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
         <v>1299</v>
       </c>
@@ -36499,7 +36500,7 @@
         <v>1814</v>
       </c>
     </row>
-    <row r="198" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
         <v>1299</v>
       </c>
@@ -36624,7 +36625,7 @@
         <v>1866</v>
       </c>
     </row>
-    <row r="199" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
         <v>1299</v>
       </c>
@@ -36764,7 +36765,7 @@
         <v>1373</v>
       </c>
     </row>
-    <row r="200" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
         <v>1299</v>
       </c>
@@ -36949,7 +36950,7 @@
         <v>1438</v>
       </c>
     </row>
-    <row r="201" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
         <v>1299</v>
       </c>
@@ -37086,7 +37087,7 @@
         <v>2454</v>
       </c>
     </row>
-    <row r="202" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
         <v>1299</v>
       </c>
@@ -37211,7 +37212,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="203" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
         <v>1299</v>
       </c>
@@ -37348,7 +37349,7 @@
         <v>1392</v>
       </c>
     </row>
-    <row r="204" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
         <v>1299</v>
       </c>
@@ -37485,7 +37486,7 @@
         <v>1731</v>
       </c>
     </row>
-    <row r="205" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
         <v>1299</v>
       </c>
@@ -37604,7 +37605,7 @@
         <v>1995</v>
       </c>
     </row>
-    <row r="206" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
         <v>1299</v>
       </c>
@@ -37741,7 +37742,7 @@
         <v>1582</v>
       </c>
     </row>
-    <row r="207" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
         <v>1299</v>
       </c>
@@ -37866,7 +37867,7 @@
         <v>2188</v>
       </c>
     </row>
-    <row r="208" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
         <v>1299</v>
       </c>
@@ -38003,7 +38004,7 @@
         <v>2459</v>
       </c>
     </row>
-    <row r="209" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
         <v>1299</v>
       </c>
@@ -38134,7 +38135,7 @@
         <v>2353</v>
       </c>
     </row>
-    <row r="210" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
         <v>1299</v>
       </c>
@@ -38265,7 +38266,7 @@
         <v>1916</v>
       </c>
     </row>
-    <row r="211" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
         <v>1299</v>
       </c>
@@ -38402,7 +38403,7 @@
         <v>1444</v>
       </c>
     </row>
-    <row r="212" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
         <v>1299</v>
       </c>
@@ -38557,7 +38558,7 @@
         <v>2061</v>
       </c>
     </row>
-    <row r="213" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
         <v>1299</v>
       </c>
@@ -38712,7 +38713,7 @@
         <v>2472</v>
       </c>
     </row>
-    <row r="214" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
         <v>1299</v>
       </c>
@@ -38870,7 +38871,7 @@
         <v>1566</v>
       </c>
     </row>
-    <row r="215" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
         <v>1299</v>
       </c>
@@ -38998,7 +38999,7 @@
         <v>2128</v>
       </c>
     </row>
-    <row r="216" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
         <v>1299</v>
       </c>
@@ -39129,7 +39130,7 @@
         <v>1634</v>
       </c>
     </row>
-    <row r="217" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
         <v>1299</v>
       </c>
@@ -39287,7 +39288,7 @@
         <v>2044</v>
       </c>
     </row>
-    <row r="218" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
         <v>1299</v>
       </c>
@@ -39418,7 +39419,7 @@
         <v>1776</v>
       </c>
     </row>
-    <row r="219" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
         <v>1299</v>
       </c>
@@ -39585,7 +39586,7 @@
         <v>2082</v>
       </c>
     </row>
-    <row r="220" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
         <v>1299</v>
       </c>
@@ -39740,7 +39741,7 @@
         <v>1611</v>
       </c>
     </row>
-    <row r="221" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
         <v>1299</v>
       </c>
@@ -39865,7 +39866,7 @@
         <v>1780</v>
       </c>
     </row>
-    <row r="222" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
         <v>1299</v>
       </c>
@@ -40002,7 +40003,7 @@
         <v>1459</v>
       </c>
     </row>
-    <row r="223" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
         <v>1299</v>
       </c>
@@ -40127,7 +40128,7 @@
         <v>1452</v>
       </c>
     </row>
-    <row r="224" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
         <v>1299</v>
       </c>
@@ -40264,7 +40265,7 @@
         <v>2431</v>
       </c>
     </row>
-    <row r="225" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
         <v>1299</v>
       </c>
@@ -40422,7 +40423,7 @@
         <v>2075</v>
       </c>
     </row>
-    <row r="226" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
         <v>1299</v>
       </c>
@@ -40547,7 +40548,7 @@
         <v>1895</v>
       </c>
     </row>
-    <row r="227" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
         <v>1299</v>
       </c>
@@ -40672,7 +40673,7 @@
         <v>1964</v>
       </c>
     </row>
-    <row r="228" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
         <v>1299</v>
       </c>
@@ -40803,7 +40804,7 @@
         <v>2170</v>
       </c>
     </row>
-    <row r="229" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
         <v>1299</v>
       </c>
@@ -40928,7 +40929,7 @@
         <v>2281</v>
       </c>
     </row>
-    <row r="230" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
         <v>1299</v>
       </c>
@@ -41065,7 +41066,7 @@
         <v>1357</v>
       </c>
     </row>
-    <row r="231" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
         <v>1299</v>
       </c>
@@ -41184,7 +41185,7 @@
         <v>1595</v>
       </c>
     </row>
-    <row r="232" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
         <v>1299</v>
       </c>
@@ -41333,7 +41334,7 @@
         <v>1571</v>
       </c>
     </row>
-    <row r="233" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
         <v>1299</v>
       </c>
@@ -41515,7 +41516,7 @@
         <v>2122</v>
       </c>
     </row>
-    <row r="234" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
         <v>1299</v>
       </c>
@@ -41652,7 +41653,7 @@
         <v>1900</v>
       </c>
     </row>
-    <row r="235" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
         <v>1299</v>
       </c>
@@ -41819,7 +41820,7 @@
         <v>1403</v>
       </c>
     </row>
-    <row r="236" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
         <v>1299</v>
       </c>
@@ -41959,7 +41960,7 @@
         <v>1749</v>
       </c>
     </row>
-    <row r="237" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
         <v>1299</v>
       </c>
@@ -42087,7 +42088,7 @@
         <v>2296</v>
       </c>
     </row>
-    <row r="238" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
         <v>1299</v>
       </c>
@@ -42224,7 +42225,7 @@
         <v>1519</v>
       </c>
     </row>
-    <row r="239" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
         <v>1299</v>
       </c>
@@ -42349,7 +42350,7 @@
         <v>1529</v>
       </c>
     </row>
-    <row r="240" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
         <v>1299</v>
       </c>
@@ -42474,7 +42475,7 @@
         <v>1576</v>
       </c>
     </row>
-    <row r="241" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
         <v>1299</v>
       </c>
@@ -42599,7 +42600,7 @@
         <v>2114</v>
       </c>
     </row>
-    <row r="242" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
         <v>1299</v>
       </c>
@@ -42736,7 +42737,7 @@
         <v>2392</v>
       </c>
     </row>
-    <row r="243" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
         <v>1299</v>
       </c>
@@ -42864,7 +42865,7 @@
         <v>1502</v>
       </c>
     </row>
-    <row r="244" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
         <v>1299</v>
       </c>
@@ -42989,7 +42990,7 @@
         <v>2228</v>
       </c>
     </row>
-    <row r="245" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
         <v>1299</v>
       </c>
@@ -43120,7 +43121,7 @@
         <v>1385</v>
       </c>
     </row>
-    <row r="246" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
         <v>1299</v>
       </c>
@@ -43245,7 +43246,7 @@
         <v>2476</v>
       </c>
     </row>
-    <row r="247" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
         <v>1299</v>
       </c>
@@ -43394,7 +43395,7 @@
         <v>2375</v>
       </c>
     </row>
-    <row r="248" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
         <v>1299</v>
       </c>
@@ -43519,7 +43520,7 @@
         <v>1785</v>
       </c>
     </row>
-    <row r="249" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
         <v>1299</v>
       </c>
@@ -43638,7 +43639,7 @@
         <v>1912</v>
       </c>
     </row>
-    <row r="250" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
         <v>1299</v>
       </c>
@@ -43778,7 +43779,7 @@
         <v>1497</v>
       </c>
     </row>
-    <row r="251" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
         <v>1299</v>
       </c>
@@ -43915,7 +43916,7 @@
         <v>1525</v>
       </c>
     </row>
-    <row r="252" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
         <v>1299</v>
       </c>
@@ -44040,7 +44041,7 @@
         <v>1323</v>
       </c>
     </row>
-    <row r="253" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
         <v>1299</v>
       </c>
@@ -44165,7 +44166,7 @@
         <v>1644</v>
       </c>
     </row>
-    <row r="254" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
         <v>1299</v>
       </c>
@@ -44296,7 +44297,7 @@
         <v>1921</v>
       </c>
     </row>
-    <row r="255" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
         <v>1299</v>
       </c>
@@ -44421,7 +44422,7 @@
         <v>1849</v>
       </c>
     </row>
-    <row r="256" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
         <v>1299</v>
       </c>
@@ -44552,7 +44553,7 @@
         <v>1588</v>
       </c>
     </row>
-    <row r="257" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
         <v>1299</v>
       </c>
@@ -44677,7 +44678,7 @@
         <v>1880</v>
       </c>
     </row>
-    <row r="258" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
         <v>1299</v>
       </c>
@@ -44826,7 +44827,7 @@
         <v>1412</v>
       </c>
     </row>
-    <row r="259" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
         <v>1299</v>
       </c>
@@ -44966,7 +44967,7 @@
         <v>1366</v>
       </c>
     </row>
-    <row r="260" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
         <v>1299</v>
       </c>
@@ -45097,7 +45098,7 @@
         <v>2258</v>
       </c>
     </row>
-    <row r="261" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
         <v>1299</v>
       </c>
@@ -45237,7 +45238,7 @@
         <v>1766</v>
       </c>
     </row>
-    <row r="262" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
         <v>1299</v>
       </c>
@@ -45374,7 +45375,7 @@
         <v>2166</v>
       </c>
     </row>
-    <row r="263" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
         <v>1299</v>
       </c>
@@ -45505,7 +45506,7 @@
         <v>1673</v>
       </c>
     </row>
-    <row r="264" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
         <v>1299</v>
       </c>
@@ -45636,7 +45637,7 @@
         <v>1683</v>
       </c>
     </row>
-    <row r="265" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
         <v>1299</v>
       </c>
@@ -45773,7 +45774,7 @@
         <v>2068</v>
       </c>
     </row>
-    <row r="266" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
         <v>1299</v>
       </c>
@@ -45916,7 +45917,7 @@
         <v>1483</v>
       </c>
     </row>
-    <row r="267" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
         <v>1299</v>
       </c>
@@ -46047,7 +46048,7 @@
         <v>2253</v>
       </c>
     </row>
-    <row r="268" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
         <v>1299</v>
       </c>
@@ -46187,7 +46188,7 @@
         <v>1828</v>
       </c>
     </row>
-    <row r="269" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
         <v>1299</v>
       </c>
@@ -46327,7 +46328,7 @@
         <v>2095</v>
       </c>
     </row>
-    <row r="270" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
         <v>1299</v>
       </c>
@@ -46464,7 +46465,7 @@
         <v>1861</v>
       </c>
     </row>
-    <row r="271" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
         <v>1299</v>
       </c>
@@ -46601,7 +46602,7 @@
         <v>1471</v>
       </c>
     </row>
-    <row r="272" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
         <v>1299</v>
       </c>
@@ -46732,7 +46733,7 @@
         <v>1379</v>
       </c>
     </row>
-    <row r="273" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
         <v>1299</v>
       </c>
@@ -46851,7 +46852,7 @@
         <v>2154</v>
       </c>
     </row>
-    <row r="274" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
         <v>1299</v>
       </c>
@@ -46991,7 +46992,7 @@
         <v>1667</v>
       </c>
     </row>
-    <row r="275" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
         <v>1299</v>
       </c>
@@ -47122,7 +47123,7 @@
         <v>1771</v>
       </c>
     </row>
-    <row r="276" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
         <v>1299</v>
       </c>
@@ -47262,7 +47263,7 @@
         <v>1490</v>
       </c>
     </row>
-    <row r="277" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
         <v>1299</v>
       </c>
@@ -47426,7 +47427,7 @@
         <v>2033</v>
       </c>
     </row>
-    <row r="278" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
         <v>1299</v>
       </c>
@@ -47560,7 +47561,7 @@
         <v>1873</v>
       </c>
     </row>
-    <row r="279" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
         <v>1299</v>
       </c>
@@ -47715,7 +47716,7 @@
         <v>1719</v>
       </c>
     </row>
-    <row r="280" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
         <v>1299</v>
       </c>
@@ -47855,7 +47856,7 @@
         <v>2182</v>
       </c>
     </row>
-    <row r="281" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
         <v>1299</v>
       </c>
@@ -48001,7 +48002,7 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="282" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
         <v>1299</v>
       </c>
@@ -48132,7 +48133,7 @@
         <v>2159</v>
       </c>
     </row>
-    <row r="283" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
         <v>1299</v>
       </c>
@@ -48260,7 +48261,7 @@
         <v>2327</v>
       </c>
     </row>
-    <row r="284" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
         <v>1299</v>
       </c>
@@ -48379,7 +48380,7 @@
         <v>2004</v>
       </c>
     </row>
-    <row r="285" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
         <v>1299</v>
       </c>
@@ -48498,7 +48499,7 @@
         <v>1884</v>
       </c>
     </row>
-    <row r="286" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
         <v>1299</v>
       </c>
@@ -48641,7 +48642,7 @@
         <v>2364</v>
       </c>
     </row>
-    <row r="287" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
         <v>1299</v>
       </c>
@@ -48799,7 +48800,7 @@
         <v>1425</v>
       </c>
     </row>
-    <row r="288" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
         <v>1299</v>
       </c>
@@ -48948,7 +48949,7 @@
         <v>2383</v>
       </c>
     </row>
-    <row r="289" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
         <v>1299</v>
       </c>
@@ -49088,7 +49089,7 @@
         <v>1560</v>
       </c>
     </row>
-    <row r="290" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
         <v>1299</v>
       </c>
@@ -49219,7 +49220,7 @@
         <v>2217</v>
       </c>
     </row>
-    <row r="291" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
         <v>1299</v>
       </c>
@@ -49413,7 +49414,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="292" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
         <v>1299</v>
       </c>
@@ -49532,7 +49533,7 @@
         <v>2009</v>
       </c>
     </row>
-    <row r="293" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
         <v>1299</v>
       </c>
@@ -49663,7 +49664,7 @@
         <v>1712</v>
       </c>
     </row>
-    <row r="294" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
         <v>1299</v>
       </c>
@@ -49782,7 +49783,7 @@
         <v>2387</v>
       </c>
     </row>
-    <row r="295" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
         <v>1299</v>
       </c>
@@ -49958,7 +49959,7 @@
         <v>1340</v>
       </c>
     </row>
-    <row r="296" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
         <v>1299</v>
       </c>
@@ -50089,7 +50090,7 @@
         <v>1694</v>
       </c>
     </row>
-    <row r="297" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
         <v>1299</v>
       </c>
@@ -50232,7 +50233,7 @@
         <v>1891</v>
       </c>
     </row>
-    <row r="298" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
         <v>1299</v>
       </c>
@@ -50363,7 +50364,7 @@
         <v>1979</v>
       </c>
     </row>
-    <row r="299" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
         <v>1299</v>
       </c>
@@ -50488,7 +50489,7 @@
         <v>1546</v>
       </c>
     </row>
-    <row r="300" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
         <v>1299</v>
       </c>
@@ -50634,7 +50635,7 @@
         <v>2304</v>
       </c>
     </row>
-    <row r="301" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
         <v>1299</v>
       </c>
@@ -50771,7 +50772,7 @@
         <v>1760</v>
       </c>
     </row>
-    <row r="302" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
         <v>1299</v>
       </c>
@@ -50908,7 +50909,7 @@
         <v>1329</v>
       </c>
     </row>
-    <row r="303" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
         <v>1299</v>
       </c>
@@ -51039,7 +51040,7 @@
         <v>1660</v>
       </c>
     </row>
-    <row r="304" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
         <v>1299</v>
       </c>
@@ -51164,7 +51165,7 @@
         <v>1649</v>
       </c>
     </row>
-    <row r="305" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
         <v>1299</v>
       </c>
@@ -51301,7 +51302,7 @@
         <v>2371</v>
       </c>
     </row>
-    <row r="306" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
         <v>1299</v>
       </c>
@@ -51417,7 +51418,7 @@
         <v>2212</v>
       </c>
     </row>
-    <row r="307" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
         <v>1299</v>
       </c>
@@ -51533,7 +51534,7 @@
         <v>1535</v>
       </c>
     </row>
-    <row r="308" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A308" t="s">
         <v>1299</v>
       </c>
@@ -51658,7 +51659,7 @@
         <v>2332</v>
       </c>
     </row>
-    <row r="309" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
         <v>1299</v>
       </c>
@@ -51804,7 +51805,7 @@
         <v>2195</v>
       </c>
     </row>
-    <row r="310" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A310" t="s">
         <v>1299</v>
       </c>
@@ -51932,7 +51933,7 @@
         <v>1992</v>
       </c>
     </row>
-    <row r="311" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
         <v>1299</v>
       </c>
@@ -52060,7 +52061,7 @@
         <v>1418</v>
       </c>
     </row>
-    <row r="312" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A312" t="s">
         <v>1299</v>
       </c>
@@ -52191,7 +52192,7 @@
         <v>1639</v>
       </c>
     </row>
-    <row r="313" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A313" t="s">
         <v>1299</v>
       </c>
@@ -52301,7 +52302,7 @@
         <v>1999</v>
       </c>
     </row>
-    <row r="314" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A314" t="s">
         <v>1299</v>
       </c>
@@ -52408,7 +52409,7 @@
         <v>1954</v>
       </c>
     </row>
-    <row r="315" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A315" t="s">
         <v>1299</v>
       </c>
@@ -52515,7 +52516,7 @@
         <v>1967</v>
       </c>
     </row>
-    <row r="316" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A316" t="s">
         <v>1299</v>
       </c>
@@ -52628,7 +52629,7 @@
         <v>2290</v>
       </c>
     </row>
-    <row r="317" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A317" t="s">
         <v>1299</v>
       </c>
@@ -52747,7 +52748,7 @@
         <v>2448</v>
       </c>
     </row>
-    <row r="318" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A318" t="s">
         <v>1299</v>
       </c>
@@ -52872,7 +52873,7 @@
         <v>1464</v>
       </c>
     </row>
-    <row r="319" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A319" t="s">
         <v>1299</v>
       </c>
@@ -52991,7 +52992,7 @@
         <v>2104</v>
       </c>
     </row>
-    <row r="320" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A320" t="s">
         <v>1299</v>
       </c>
@@ -53110,7 +53111,7 @@
         <v>2357</v>
       </c>
     </row>
-    <row r="321" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A321" t="s">
         <v>1299</v>
       </c>
@@ -53238,7 +53239,7 @@
         <v>1699</v>
       </c>
     </row>
-    <row r="322" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A322" t="s">
         <v>1299</v>
       </c>
@@ -53363,7 +53364,7 @@
         <v>1448</v>
       </c>
     </row>
-    <row r="323" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A323" t="s">
         <v>1299</v>
       </c>
@@ -53482,7 +53483,7 @@
         <v>1805</v>
       </c>
     </row>
-    <row r="324" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A324" t="s">
         <v>1299</v>
       </c>
@@ -53610,7 +53611,7 @@
         <v>2150</v>
       </c>
     </row>
-    <row r="325" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A325" t="s">
         <v>1299</v>
       </c>
@@ -53726,7 +53727,7 @@
         <v>1604</v>
       </c>
     </row>
-    <row r="326" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A326" t="s">
         <v>1299</v>
       </c>
@@ -53839,7 +53840,7 @@
         <v>2309</v>
       </c>
     </row>
-    <row r="327" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A327" t="s">
         <v>1299</v>
       </c>
@@ -53970,7 +53971,7 @@
         <v>2316</v>
       </c>
     </row>
-    <row r="328" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A328" t="s">
         <v>1299</v>
       </c>
@@ -54095,7 +54096,7 @@
         <v>2322</v>
       </c>
     </row>
-    <row r="329" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A329" t="s">
         <v>1299</v>
       </c>
@@ -54211,7 +54212,7 @@
         <v>2264</v>
       </c>
     </row>
-    <row r="330" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A330" t="s">
         <v>1299</v>
       </c>
@@ -54348,7 +54349,7 @@
         <v>1844</v>
       </c>
     </row>
-    <row r="331" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A331" t="s">
         <v>1299</v>
       </c>
@@ -54479,7 +54480,7 @@
         <v>2088</v>
       </c>
     </row>
-    <row r="332" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A332" t="s">
         <v>1299</v>
       </c>
@@ -54607,7 +54608,7 @@
         <v>1617</v>
       </c>
     </row>
-    <row r="333" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A333" t="s">
         <v>1299</v>
       </c>
@@ -54741,7 +54742,7 @@
         <v>2208</v>
       </c>
     </row>
-    <row r="334" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A334" t="s">
         <v>1299</v>
       </c>
@@ -54875,7 +54876,7 @@
         <v>2235</v>
       </c>
     </row>
-    <row r="335" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A335" t="s">
         <v>1299</v>
       </c>
@@ -54994,7 +54995,7 @@
         <v>1951</v>
       </c>
     </row>
-    <row r="336" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A336" t="s">
         <v>1299</v>
       </c>
@@ -55110,7 +55111,7 @@
         <v>1931</v>
       </c>
     </row>
-    <row r="337" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A337" t="s">
         <v>1299</v>
       </c>
@@ -55235,7 +55236,7 @@
         <v>1960</v>
       </c>
     </row>
-    <row r="338" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A338" t="s">
         <v>1299</v>
       </c>
@@ -55348,7 +55349,7 @@
         <v>1723</v>
       </c>
     </row>
-    <row r="339" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A339" t="s">
         <v>1299</v>
       </c>
@@ -55470,7 +55471,7 @@
         <v>2055</v>
       </c>
     </row>
-    <row r="340" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A340" t="s">
         <v>1299</v>
       </c>
@@ -55592,7 +55593,7 @@
         <v>1973</v>
       </c>
     </row>
-    <row r="341" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A341" t="s">
         <v>1299</v>
       </c>
@@ -55720,7 +55721,7 @@
         <v>1623</v>
       </c>
     </row>
-    <row r="342" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A342" t="s">
         <v>1299</v>
       </c>
@@ -55851,7 +55852,7 @@
         <v>1348</v>
       </c>
     </row>
-    <row r="343" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A343" t="s">
         <v>1299</v>
       </c>
@@ -55970,7 +55971,7 @@
         <v>2136</v>
       </c>
     </row>
-    <row r="344" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A344" t="s">
         <v>1299</v>
       </c>
@@ -56089,7 +56090,7 @@
         <v>2286</v>
       </c>
     </row>
-    <row r="345" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A345" t="s">
         <v>1299</v>
       </c>
@@ -56202,7 +56203,7 @@
         <v>1313</v>
       </c>
     </row>
-    <row r="346" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A346" t="s">
         <v>1299</v>
       </c>
@@ -56324,7 +56325,7 @@
         <v>1688</v>
       </c>
     </row>
-    <row r="347" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A347" t="s">
         <v>1299</v>
       </c>
@@ -56458,7 +56459,7 @@
         <v>1946</v>
       </c>
     </row>
-    <row r="348" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A348" t="s">
         <v>1299</v>
       </c>
@@ -56589,7 +56590,7 @@
         <v>2201</v>
       </c>
     </row>
-    <row r="349" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A349" t="s">
         <v>1299</v>
       </c>
@@ -56699,7 +56700,7 @@
         <v>1926</v>
       </c>
     </row>
-    <row r="350" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A350" t="s">
         <v>1299</v>
       </c>
@@ -56812,7 +56813,7 @@
         <v>2175</v>
       </c>
     </row>
-    <row r="351" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A351" t="s">
         <v>1299</v>
       </c>
@@ -56928,7 +56929,7 @@
         <v>2337</v>
       </c>
     </row>
-    <row r="352" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A352" t="s">
         <v>1299</v>
       </c>
@@ -57047,7 +57048,7 @@
         <v>1799</v>
       </c>
     </row>
-    <row r="353" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A353" t="s">
         <v>1299</v>
       </c>
@@ -57181,7 +57182,7 @@
         <v>1986</v>
       </c>
     </row>
-    <row r="354" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A354" t="s">
         <v>1299</v>
       </c>
@@ -57300,7 +57301,7 @@
         <v>2405</v>
       </c>
     </row>
-    <row r="355" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A355" t="s">
         <v>1299</v>
       </c>
@@ -57422,7 +57423,7 @@
         <v>2411</v>
       </c>
     </row>
-    <row r="356" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A356" t="s">
         <v>1299</v>
       </c>
@@ -57559,7 +57560,7 @@
         <v>2437</v>
       </c>
     </row>
-    <row r="357" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A357" t="s">
         <v>1299</v>
       </c>
@@ -57690,7 +57691,7 @@
         <v>1877</v>
       </c>
     </row>
-    <row r="358" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A358" t="s">
         <v>1299</v>
       </c>
@@ -57830,7 +57831,7 @@
         <v>2344</v>
       </c>
     </row>
-    <row r="359" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A359" t="s">
         <v>1299</v>
       </c>
@@ -57967,7 +57968,7 @@
         <v>2269</v>
       </c>
     </row>
-    <row r="360" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A360" t="s">
         <v>1299</v>
       </c>
@@ -58125,7 +58126,7 @@
         <v>2444</v>
       </c>
     </row>
-    <row r="361" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A361" t="s">
         <v>1299</v>
       </c>
@@ -58256,7 +58257,7 @@
         <v>2348</v>
       </c>
     </row>
-    <row r="362" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A362" t="s">
         <v>1299</v>
       </c>
@@ -58402,7 +58403,7 @@
         <v>1909</v>
       </c>
     </row>
-    <row r="363" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A363" t="s">
         <v>1299</v>
       </c>
@@ -58527,7 +58528,7 @@
         <v>1678</v>
       </c>
     </row>
-    <row r="364" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A364" t="s">
         <v>1299</v>
       </c>
@@ -58667,7 +58668,7 @@
         <v>2111</v>
       </c>
     </row>
-    <row r="365" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A365" t="s">
         <v>1299</v>
       </c>
@@ -58813,7 +58814,7 @@
         <v>2400</v>
       </c>
     </row>
-    <row r="366" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A366" t="s">
         <v>1299</v>
       </c>
@@ -58950,7 +58951,7 @@
         <v>2466</v>
       </c>
     </row>
-    <row r="367" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A367" t="s">
         <v>1299</v>
       </c>
@@ -59081,7 +59082,7 @@
         <v>1743</v>
       </c>
     </row>
-    <row r="368" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A368" t="s">
         <v>1299</v>
       </c>
@@ -59218,7 +59219,7 @@
         <v>1821</v>
       </c>
     </row>
-    <row r="369" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A369" t="s">
         <v>1299</v>
       </c>
@@ -59352,7 +59353,7 @@
         <v>2425</v>
       </c>
     </row>
-    <row r="370" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A370" t="s">
         <v>1299</v>
       </c>
@@ -59489,7 +59490,7 @@
         <v>2276</v>
       </c>
     </row>
-    <row r="371" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A371" t="s">
         <v>1299</v>
       </c>
@@ -59620,7 +59621,7 @@
         <v>1853</v>
       </c>
     </row>
-    <row r="372" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A372" t="s">
         <v>1299</v>
       </c>
@@ -59745,7 +59746,7 @@
         <v>2049</v>
       </c>
     </row>
-    <row r="373" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A373" t="s">
         <v>1299</v>
       </c>
@@ -59885,7 +59886,7 @@
         <v>1939</v>
       </c>
     </row>
-    <row r="374" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A374" t="s">
         <v>1299</v>
       </c>
@@ -60022,7 +60023,7 @@
         <v>2144</v>
       </c>
     </row>
-    <row r="375" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A375" t="s">
         <v>1299</v>
       </c>
@@ -60162,7 +60163,7 @@
         <v>2419</v>
       </c>
     </row>
-    <row r="376" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="376" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A376" t="s">
         <v>1299</v>
       </c>
@@ -60311,7 +60312,7 @@
         <v>1793</v>
       </c>
     </row>
-    <row r="377" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
       <c r="A377" t="s">
         <v>72</v>
       </c>
@@ -60444,6 +60445,11 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:BU377" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="Nacala Porto"/>
+      </filters>
+    </filterColumn>
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:BU377">
       <sortCondition ref="BU1:BU377"/>
     </sortState>
@@ -60453,26 +60459,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="54c5ab46-7543-4aba-b0fa-79d6a199bef5" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="20d57abc-823c-4051-a81a-1a0a01a8f39e">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100DC8BB5B596CFDD4794B3344F0E8F53A4" ma:contentTypeVersion="15" ma:contentTypeDescription="Criar um novo documento." ma:contentTypeScope="" ma:versionID="9a7078cd21229583650f2264465a1c40">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="20d57abc-823c-4051-a81a-1a0a01a8f39e" xmlns:ns3="54c5ab46-7543-4aba-b0fa-79d6a199bef5" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4e45437c47114f519c494620e3e4bb67" ns2:_="" ns3:_="">
     <xsd:import namespace="20d57abc-823c-4051-a81a-1a0a01a8f39e"/>
@@ -60707,10 +60693,41 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="54c5ab46-7543-4aba-b0fa-79d6a199bef5" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="20d57abc-823c-4051-a81a-1a0a01a8f39e">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7703B566-3A82-4514-9901-3E0C0621FFDB}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4D10A5D0-F2A1-46C5-BD5C-3D0BDFB2142B}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="20d57abc-823c-4051-a81a-1a0a01a8f39e"/>
+    <ds:schemaRef ds:uri="54c5ab46-7543-4aba-b0fa-79d6a199bef5"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -60727,20 +60744,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4D10A5D0-F2A1-46C5-BD5C-3D0BDFB2142B}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7703B566-3A82-4514-9901-3E0C0621FFDB}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="20d57abc-823c-4051-a81a-1a0a01a8f39e"/>
-    <ds:schemaRef ds:uri="54c5ab46-7543-4aba-b0fa-79d6a199bef5"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>